--- a/validated_jama_test_cases.xlsx
+++ b/validated_jama_test_cases.xlsx
@@ -64,7 +64,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -431,14 +431,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
@@ -447,7 +447,7 @@
     <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="50" customHeight="1">
+    <row r="1" ht="120" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Test Run ID</t>
@@ -504,7 +504,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="120" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>US-33382</t>
@@ -525,27 +525,32 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Login Page</t>
+          <t>Salesforce Login</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Navigate to Salesforce URL</t>
+          <t>1) Open a web browser
+2) Enter the GEHC Salesforce URL: ga-healthcare.test.sandbox.salesforce.com
+3) Use valid SSO credentials for manish.batta@gehc.svc.test
+4) Navigate to the Production Sandbox environment.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Salesforce login screen is displayed.</t>
+          <t>1) System redirects to the Salesforce Home Page dashboard.
+2) User ID manish.batta@gehc.svc.test is visible in the profile section.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Salesforce login screen displayed successfully.</t>
+          <t>1) Salesforce URL ga-healthcare.test.sandbox.salesforce.com opened.
+2) manish.batta@gehc.svc.test logged in successfully at 09:05 AM.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>No Objective Evidence is required / attached</t>
+          <t>evidence/scenario_login.png</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -556,63 +561,44 @@
       <c r="K2" s="3" t="inlineStr">
         <is>
           <t>[PASS] Action context matches Expected and Actual results
-└─ Mapped Keywords Verified: salesforce</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>US-33382</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>TC-7686</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>REQ-3506</t>
-        </is>
-      </c>
+Mapped Keywords: test, gehc, manish, svc, salesforce, batta
+[PASS] UI Context: Salesforce Login
+[PASS] Salesforce URL verified: ga-healthcare.test.sandbox.salesforce.com
+[PASS] Tester ID verified: manish.batta@gehc.svc.test
+[PASS] Timestamp: 2026-03-17 09:05:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="120" customHeight="1">
       <c r="D3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Home Page</t>
+          <t>FSL Home</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Login to Salesforce
-1) Open a web browser
-2) Record Salesforce URL
-3) Use Tester's id and valid password credentials to log into Salesforce.com
-4) Record Tester ID, Login Date, time and time zone</t>
+          <t>1) In the Global Search bar, type the Work Order ID: WO-00293847
+2) Select the matching record from the search results dropping down.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>1) Web browser is opened
-2) Salesforce URL is recorded https://gehealthcare.svc--test.sandbox.my.salesforce.com
-3) Tester is logged into Salesforce.com.
-4) Tester ID, Login Date, time and time zone are recorded</t>
+          <t>1) Work Order WO-00293847 is successfully retrieved.
+2) The page header displays the correct Work Order number.</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>1) Web browser was opened.
-2) Salesforce URL was recorded https://gehealthcare.svc--test.sandbox.my.salesforce.com
-3) Tester was logged into Salesforce.com.
-4) Tester ID, Login Date, time and time zone was recorded
-(manish.batta@gehc.svc.test 03-Feb-2026 5:18 PM IST)</t>
+          <t>1) Search for WO-00293847 returned 1 match.
+2) Work Order record detail view loaded.</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>evidence/jama_login_shadow.png</t>
+          <t>no objective evidence is required / attached</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -623,56 +609,40 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>[PASS] Action context matches Expected and Actual results
-└─ Mapped Keywords Verified: log, into, time, date, open, browser, record, url, login, salesforce, com, zone, web
-[PASS] UI Context verified: Home Page
-[PASS] Salesforce URL verified: gehealthcare.svc--test.sandbox.my.salesforce.com
-[PASS] Tester ID verified: manish.batta@gehc.svc.test
-[PASS] Timestamp found: 2026-02-03 17:18:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="80" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>US-33382</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>TC-7686</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>REQ-3506</t>
-        </is>
-      </c>
+Mapped Keywords: work, order, 00293847</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="120" customHeight="1">
       <c r="D4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lightning Experience</t>
+          <t>Service Work Order</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Click on "Switch to Lightning Experience" mode</t>
+          <t>1) Once the Work Order record loads, scroll down to the "Products Required" related list.
+2) Verify the list is visible and populated.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Verified that user is on Lightning mode</t>
+          <t>1) The user is navigated to the correct "Related" tab view.
+2) The "Products Required" section is rendered correctly on the screen.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Verified that user was on Lightning mode</t>
+          <t>1) Related list section found.
+2) Navigation to the list view confirmed.</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>No Objective Evidence is required / attached</t>
+          <t>no objective evidence is required / attached</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -683,110 +653,88 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>[PASS] Action context matches Expected and Actual results
-└─ Mapped Keywords Verified: lightning, mode</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="80" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>US-33382</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>TC-7686</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>REQ-3506</t>
-        </is>
-      </c>
+Mapped Keywords: related</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="120" customHeight="1">
       <c r="D5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Work Orders Tab</t>
+          <t>Related List: Parts</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Navigate to Work Orders</t>
+          <t>1) Click the "New" button in the Products Required related list title bar.
+2) Wait for the modal window to load.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Work Orders List View is displayed.</t>
+          <t>1) The "New Product Required" modal window pops up over the current view.
+2) The focus shifts to the modal fields.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Work Order WO-998877 displayed perfectly.</t>
+          <t>1) Modal window displayed.
+2) UI Context updated to Product Request Modal.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>evidence/scenario_work_order.png</t>
+          <t>no objective evidence is required / attached</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[PASS] Action context matches Expected and Actual results
-└─ Mapped Keywords Verified: work
-[PASS] Work Order verified: WO-998877
-[PASS] Timestamp found: 2026-02-23 09:12:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>US-33382</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>TC-7686</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>REQ-3506</t>
-        </is>
-      </c>
+          <t>[FAIL] Actual result lacks context from Action
+Audit Trail: window, modal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="120" customHeight="1">
       <c r="D6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Related Tab</t>
+          <t>Product Request Modal</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Create Part Request</t>
+          <t>1) Locate the SKU lookup field.
+2) Select SKU: GE-9988-X
+3) Set Quantity: 1
+4) Set Priority: "Expedited"
+5) Capture screenshot of the populated modal.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>New Part Request screen opens with required fields.</t>
+          <t>1) All mandatory fields (SKU, Qty) are correctly filled.
+2) No validation error messages appear for the "Expedited" priority.</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Part Request PR-44556 created successfully.</t>
+          <t>1) SKU GE-9988-X successfully selected.
+2) Quantity set to 1.
+3) Screenshot captured: evidence/scenario_work_order.png</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>evidence/scenario_part_request_created.png</t>
+          <t>evidence/scenario_work_order.png</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -797,12 +745,241 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>[PASS] Action context matches Expected and Actual results
-└─ Mapped Keywords Verified: part, request
-[PASS] Timestamp found: 2026-02-23 09:17:00</t>
+Mapped Keywords: sku
+[PASS] UI Context: Product Request Modal
+[PASS] Timestamp: 2026-03-17 09:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="120" customHeight="1">
+      <c r="D7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Product Request Detail</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>1) Click "Save" on the modal.
+2) Verify the new PR-445566 record appears in the list.
+3) Capture screenshot of the record detail view.</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>1) The Product Request (PR-445566) is successfully saved.
+2) The record is visible in the parent Work Order Related List.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>1) PR-445566 saved successfully.
+2) Record visible in the list.
+3) Screenshot captured: evidence/scenario_pr_status.png</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>evidence/scenario_pr_status.png</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>[PASS] Action context matches Expected and Actual results
+Mapped Keywords: record, 445566, list, save
+[PASS] UI Context: Product Request Detail
+[PASS] Timestamp: 2026-03-17 09:20:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="D8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Stock Transfer Page</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>1) Navigate to the Stock Transfer sub-tab.
+2) Click "Transfer Inventory" button.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>1) Transfer modal opens correctly.
+2) Source warehouse "Global Depo" is autopopulated.</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>1) Navigated to Transfer sub-tab.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>no objective evidence is required / attached</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>[PASS] Action context matches Expected and Actual results
+Mapped Keywords: transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="120" customHeight="1">
+      <c r="D9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Shipment Detail</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>1) Verify Shipment track number SHP-001928 is correctly generated.
+2) Check for "Shipped" status tag.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>1) Status changes to "Shipped".
+2) Transit time estimated at 24 hours.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>1) SHP-001928 generated.
+2) Status: Shipped.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>no objective evidence is required / attached</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>[FAIL] Expected result lacks context from Action
+Audit Trail: shipped, status</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="120" customHeight="1">
+      <c r="D10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Inventory Ledger</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>1) Open the Inventory Ledger view.
+2) Search for Part: GE-9988-X to verify deduction.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>1) Ledger shows -1 unit for GE-9988-X.
+2) Remaining stock: 49 units.</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>1) Part deduction confirmed for GE-9988-X.
+2) Deduction shown in ledger.</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>no objective evidence is required / attached</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>[PASS] Action context matches Expected and Actual results
+Mapped Keywords: ledger, 9988</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="120" customHeight="1">
+      <c r="D11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Test Close</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>1) Finalize the test execution.
+2) Record total duration and sign off.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>1) Test run status set to "Complete".
+2) All evidence files attached successfully.</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>1) Execution finalized at 11:30 AM.
+2) Sign off completed by manish.batta.</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>no objective evidence is required / attached</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>[FAIL] Expected result lacks context from Action
+Audit Trail: None</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C2:C11"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="A2:A11"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>